--- a/data/config/luban/config/general/default_item.xlsx
+++ b/data/config/luban/config/general/default_item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="17610" windowHeight="6315"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>##var</t>
   </si>
@@ -44,6 +44,9 @@
     <t>player_item</t>
   </si>
   <si>
+    <t>wear</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -53,6 +56,9 @@
     <t>list#sep=|,item</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -63,6 +69,9 @@
   </si>
   <si>
     <t>默认物品</t>
+  </si>
+  <si>
+    <t>是否穿戴</t>
   </si>
   <si>
     <t>400001;1|500001;1|600001;1</t>
@@ -1259,8 +1268,8 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
@@ -1270,7 +1279,7 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1283,52 +1292,67 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:4">
+    <row r="2" s="1" customFormat="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:4">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:4">
+    <row r="4" s="2" customFormat="1" spans="1:5">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="B5" s="2">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/config/luban/config/general/default_item.xlsx
+++ b/data/config/luban/config/general/default_item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="17610" windowHeight="6315"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -74,13 +74,13 @@
     <t>是否穿戴</t>
   </si>
   <si>
-    <t>400001;1|500001;1|600001;1</t>
+    <t>4011001;1|5011001;1|6011001;1</t>
   </si>
   <si>
     <t>默认黄金</t>
   </si>
   <si>
-    <t>100001;100|100002;1000|100003;10000</t>
+    <t>1001001;100|1001002;1000|1001003;10000</t>
   </si>
 </sst>
 </file>

--- a/data/config/luban/config/general/default_item.xlsx
+++ b/data/config/luban/config/general/default_item.xlsx
@@ -74,7 +74,7 @@
     <t>是否穿戴</t>
   </si>
   <si>
-    <t>4011001;1|5011001;1|6011001;1</t>
+    <t>4011001;1|5001001;1|6001001;1</t>
   </si>
   <si>
     <t>默认黄金</t>

--- a/data/config/luban/config/general/default_item.xlsx
+++ b/data/config/luban/config/general/default_item.xlsx
@@ -74,7 +74,7 @@
     <t>是否穿戴</t>
   </si>
   <si>
-    <t>4011001;1|5001001;1|6001001;1</t>
+    <t>4011001;1|5011001;1|6001001;1</t>
   </si>
   <si>
     <t>默认黄金</t>

--- a/data/config/luban/config/general/default_item.xlsx
+++ b/data/config/luban/config/general/default_item.xlsx
@@ -74,7 +74,7 @@
     <t>是否穿戴</t>
   </si>
   <si>
-    <t>4011001;1|5011001;1|6001001;1</t>
+    <t>4011001;1|5011001;1</t>
   </si>
   <si>
     <t>默认黄金</t>
